--- a/planilha fechamento.xlsx
+++ b/planilha fechamento.xlsx
@@ -1,110 +1,77 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t xml:space="preserve">Nome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vencimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data pagamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Método pagamento</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="6">
     <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b val="true"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
@@ -112,57 +79,116 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -273,53 +299,372 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G1048576"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.98"/>
+    <col width="20.26" customWidth="1" style="4" min="1" max="1"/>
+    <col width="14.09" customWidth="1" style="4" min="3" max="3"/>
+    <col width="14.48" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16.98" customWidth="1" style="4" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1" ht="13.5" customHeight="1" s="5">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Nome</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>CPF</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Vencimento</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Data pagamento</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Método pagamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Noah da Mota</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>747.91</v>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>472.963.815-82</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>07/04/2024</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Santos</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>231.659.708-40</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>07/12/2024</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Noah da Mota</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>747.91</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>472.963.815-82</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>07/04/2024</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Carlos Eduardo Santos</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>231.659.708-40</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>07/12/2024</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Felipe Farias</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>285.56</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>487.039.126-04</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>07/02/2024</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Luigi Barros</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>349.87</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>179.432.680-40</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>29/06/2024</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Stella da Luz</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>449.42</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>821.074.653-71</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>16/07/2024</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Elisa da Cunha</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>655.34</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>281.597.640-49</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>07/05/2024</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Rodrigo Fernandes</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>615.39</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>358.170.962-77</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>13/07/2024</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Dra. Alícia Monteiro</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>726.4299999999999</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>098.132.475-41</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>26/06/2024</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Eduardo Farias</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>370.38</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>203.546.178-26</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>23/06/2024</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Dr. Gustavo Costa</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>949.45</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>916.253.408-42</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>07/12/2024</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048573" ht="12.8" customHeight="1" s="5"/>
+    <row r="1048574" ht="12.8" customHeight="1" s="5"/>
+    <row r="1048575" ht="12.8" customHeight="1" s="5"/>
+    <row r="1048576" ht="12.8" customHeight="1" s="5"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 Page &amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>